--- a/owlcms/src/main/resources/agegroups/FHQ-AgeGroups_fr_CA.xlsx
+++ b/owlcms/src/main/resources/agegroups/FHQ-AgeGroups_fr_CA.xlsx
@@ -1,18 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\agegroups\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{438E77CC-7BA8-4990-954E-452544B4FE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="BW Categories" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="AgeGroups" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="BW Categories" sheetId="1" r:id="rId1"/>
+    <sheet name="AgeGroups" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -21,596 +35,585 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="186">
-  <si>
-    <t xml:space="preserve">code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_bw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WR_SR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WR_JR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WR_YTH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://en.wikipedia.org/wiki/List_of_world_records_in_Olympic_weightlifting#Men</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://en.wikipedia.org/wiki/List_of_junior_world_records_in_Olympic_weightlifting#Men</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M999 is always used as the last category in an age group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F999 is always used as the last category in an age group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">championshipName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">from</t>
-  </si>
-  <si>
-    <t xml:space="preserve">to</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#bodyweight categories or each age group (bodyweight category code followed by optional qualifying total, example: 45 80)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F40 36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F45 41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F49 49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F55 53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F59 57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F64 60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F71 63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F999 67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F40 35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F45 40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F49 44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F55 50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F59 54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F64 59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F71 66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F999 70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Louis-Cyr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F45 46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F49 54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F55 58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F59 63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F64 67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F71 71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F76 75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F999 79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Etudiant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F45 51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F49 57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F55 65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F59 72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F64 79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F71 87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F76 91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F999 94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collégial-Universitaire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F45 85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F49 97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F55 104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F59 112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F64 117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F71 118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F76 123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F81 124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F87 125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F999 135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maîtres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MASTERS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YTH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeunesse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IWF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F45 118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F49 126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F55 137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F59 144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F64 151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F71 160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F76 167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F81 172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F87 177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F999 186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OPEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ouvert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEFAULT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M40 36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M45 41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M49 49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M55 53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M61 59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M67 64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M73 68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M999 72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M40 35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M45 40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M49 44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M55 50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M61 56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M67 62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M45 49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M49 54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M55 60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M61 67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M67 72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M73 78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M81 84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M999 90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M49 62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M55 72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M61 80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M67 89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M73 95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M81 103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M89 110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M999 115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M55 130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M61 146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M67 159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M73 169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M81 177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M89 181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M96 192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M102 194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M109 196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M999 208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M55 182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M61 198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M67 210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M73 223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M81 237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M89 249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M96 257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M102 265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M109 271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M999 284</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="189">
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>max_bw</t>
+  </si>
+  <si>
+    <t>WR_SR</t>
+  </si>
+  <si>
+    <t>WR_JR</t>
+  </si>
+  <si>
+    <t>WR_YTH</t>
+  </si>
+  <si>
+    <t>M35</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>https://en.wikipedia.org/wiki/List_of_world_records_in_Olympic_weightlifting#Men</t>
+  </si>
+  <si>
+    <t>M40</t>
+  </si>
+  <si>
+    <t>https://en.wikipedia.org/wiki/List_of_junior_world_records_in_Olympic_weightlifting#Men</t>
+  </si>
+  <si>
+    <t>M45</t>
+  </si>
+  <si>
+    <t>M49</t>
+  </si>
+  <si>
+    <t>M55</t>
+  </si>
+  <si>
+    <t>M61</t>
+  </si>
+  <si>
+    <t>M67</t>
+  </si>
+  <si>
+    <t>M73</t>
+  </si>
+  <si>
+    <t>M81</t>
+  </si>
+  <si>
+    <t>M89</t>
+  </si>
+  <si>
+    <t>M96</t>
+  </si>
+  <si>
+    <t>M102</t>
+  </si>
+  <si>
+    <t>M109</t>
+  </si>
+  <si>
+    <t>M999</t>
+  </si>
+  <si>
+    <t>M999 is always used as the last category in an age group</t>
+  </si>
+  <si>
+    <t>F35</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>F40</t>
+  </si>
+  <si>
+    <t>F45</t>
+  </si>
+  <si>
+    <t>F49</t>
+  </si>
+  <si>
+    <t>F55</t>
+  </si>
+  <si>
+    <t>F59</t>
+  </si>
+  <si>
+    <t>F64</t>
+  </si>
+  <si>
+    <t>F71</t>
+  </si>
+  <si>
+    <t>F76</t>
+  </si>
+  <si>
+    <t>F81</t>
+  </si>
+  <si>
+    <t>F87</t>
+  </si>
+  <si>
+    <t>F999</t>
+  </si>
+  <si>
+    <t>F999 is always used as the last category in an age group</t>
+  </si>
+  <si>
+    <t>championshipName</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>from</t>
+  </si>
+  <si>
+    <t>to</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>#bodyweight categories or each age group (bodyweight category code followed by optional qualifying total, example: 45 80)</t>
+  </si>
+  <si>
+    <t>U10</t>
+  </si>
+  <si>
+    <t>U12</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>Mini</t>
+  </si>
+  <si>
+    <t>F40 36</t>
+  </si>
+  <si>
+    <t>F45 41</t>
+  </si>
+  <si>
+    <t>F49 49</t>
+  </si>
+  <si>
+    <t>F55 53</t>
+  </si>
+  <si>
+    <t>F59 57</t>
+  </si>
+  <si>
+    <t>F64 60</t>
+  </si>
+  <si>
+    <t>F71 63</t>
+  </si>
+  <si>
+    <t>F999 67</t>
+  </si>
+  <si>
+    <t>U13</t>
+  </si>
+  <si>
+    <t>F40 35</t>
+  </si>
+  <si>
+    <t>F45 40</t>
+  </si>
+  <si>
+    <t>F49 44</t>
+  </si>
+  <si>
+    <t>F55 50</t>
+  </si>
+  <si>
+    <t>F59 54</t>
+  </si>
+  <si>
+    <t>F64 59</t>
+  </si>
+  <si>
+    <t>F71 66</t>
+  </si>
+  <si>
+    <t>F999 70</t>
+  </si>
+  <si>
+    <t>LC</t>
+  </si>
+  <si>
+    <t>Louis-Cyr</t>
+  </si>
+  <si>
+    <t>F45 46</t>
+  </si>
+  <si>
+    <t>F49 54</t>
+  </si>
+  <si>
+    <t>F55 58</t>
+  </si>
+  <si>
+    <t>F59 63</t>
+  </si>
+  <si>
+    <t>F64 67</t>
+  </si>
+  <si>
+    <t>F71 71</t>
+  </si>
+  <si>
+    <t>F76 75</t>
+  </si>
+  <si>
+    <t>F999 79</t>
+  </si>
+  <si>
+    <t>U17</t>
+  </si>
+  <si>
+    <t>ET</t>
+  </si>
+  <si>
+    <t>Etudiant</t>
+  </si>
+  <si>
+    <t>F45 51</t>
+  </si>
+  <si>
+    <t>F49 57</t>
+  </si>
+  <si>
+    <t>F55 65</t>
+  </si>
+  <si>
+    <t>F59 72</t>
+  </si>
+  <si>
+    <t>F64 79</t>
+  </si>
+  <si>
+    <t>F71 87</t>
+  </si>
+  <si>
+    <t>F76 91</t>
+  </si>
+  <si>
+    <t>F999 94</t>
+  </si>
+  <si>
+    <t>CU</t>
+  </si>
+  <si>
+    <t>Collégial-Universitaire</t>
+  </si>
+  <si>
+    <t>F45 85</t>
+  </si>
+  <si>
+    <t>F49 97</t>
+  </si>
+  <si>
+    <t>F55 104</t>
+  </si>
+  <si>
+    <t>F59 112</t>
+  </si>
+  <si>
+    <t>F64 117</t>
+  </si>
+  <si>
+    <t>F71 118</t>
+  </si>
+  <si>
+    <t>F76 123</t>
+  </si>
+  <si>
+    <t>F81 124</t>
+  </si>
+  <si>
+    <t>F87 125</t>
+  </si>
+  <si>
+    <t>F999 135</t>
+  </si>
+  <si>
+    <t>F30</t>
+  </si>
+  <si>
+    <t>Maîtres</t>
+  </si>
+  <si>
+    <t>MASTERS</t>
+  </si>
+  <si>
+    <t>F50</t>
+  </si>
+  <si>
+    <t>F60</t>
+  </si>
+  <si>
+    <t>F65</t>
+  </si>
+  <si>
+    <t>F70</t>
+  </si>
+  <si>
+    <t>F75</t>
+  </si>
+  <si>
+    <t>F80</t>
+  </si>
+  <si>
+    <t>F85</t>
+  </si>
+  <si>
+    <t>YTH</t>
+  </si>
+  <si>
+    <t>Jeunesse</t>
+  </si>
+  <si>
+    <t>IWF</t>
+  </si>
+  <si>
+    <t>JR</t>
+  </si>
+  <si>
+    <t>Junior</t>
+  </si>
+  <si>
+    <t>SR</t>
+  </si>
+  <si>
+    <t>Senior</t>
+  </si>
+  <si>
+    <t>F45 118</t>
+  </si>
+  <si>
+    <t>F49 126</t>
+  </si>
+  <si>
+    <t>F55 137</t>
+  </si>
+  <si>
+    <t>F59 144</t>
+  </si>
+  <si>
+    <t>F64 151</t>
+  </si>
+  <si>
+    <t>F71 160</t>
+  </si>
+  <si>
+    <t>F76 167</t>
+  </si>
+  <si>
+    <t>F81 172</t>
+  </si>
+  <si>
+    <t>F87 177</t>
+  </si>
+  <si>
+    <t>F999 186</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>Ouvert</t>
+  </si>
+  <si>
+    <t>DEFAULT</t>
+  </si>
+  <si>
+    <t>M40 36</t>
+  </si>
+  <si>
+    <t>M45 41</t>
+  </si>
+  <si>
+    <t>M49 49</t>
+  </si>
+  <si>
+    <t>M55 53</t>
+  </si>
+  <si>
+    <t>M61 59</t>
+  </si>
+  <si>
+    <t>M67 64</t>
+  </si>
+  <si>
+    <t>M73 68</t>
+  </si>
+  <si>
+    <t>M999 72</t>
+  </si>
+  <si>
+    <t>M40 35</t>
+  </si>
+  <si>
+    <t>M45 40</t>
+  </si>
+  <si>
+    <t>M49 44</t>
+  </si>
+  <si>
+    <t>M55 50</t>
+  </si>
+  <si>
+    <t>M61 56</t>
+  </si>
+  <si>
+    <t>M67 62</t>
+  </si>
+  <si>
+    <t>M45 49</t>
+  </si>
+  <si>
+    <t>M49 54</t>
+  </si>
+  <si>
+    <t>M55 60</t>
+  </si>
+  <si>
+    <t>M61 67</t>
+  </si>
+  <si>
+    <t>M67 72</t>
+  </si>
+  <si>
+    <t>M73 78</t>
+  </si>
+  <si>
+    <t>M81 84</t>
+  </si>
+  <si>
+    <t>M999 90</t>
+  </si>
+  <si>
+    <t>M49 62</t>
+  </si>
+  <si>
+    <t>M55 72</t>
+  </si>
+  <si>
+    <t>M61 80</t>
+  </si>
+  <si>
+    <t>M67 89</t>
+  </si>
+  <si>
+    <t>M73 95</t>
+  </si>
+  <si>
+    <t>M81 103</t>
+  </si>
+  <si>
+    <t>M89 110</t>
+  </si>
+  <si>
+    <t>M999 115</t>
+  </si>
+  <si>
+    <t>M55 130</t>
+  </si>
+  <si>
+    <t>M61 146</t>
+  </si>
+  <si>
+    <t>M67 159</t>
+  </si>
+  <si>
+    <t>M73 169</t>
+  </si>
+  <si>
+    <t>M81 177</t>
+  </si>
+  <si>
+    <t>M89 181</t>
+  </si>
+  <si>
+    <t>M96 192</t>
+  </si>
+  <si>
+    <t>M102 194</t>
+  </si>
+  <si>
+    <t>M109 196</t>
+  </si>
+  <si>
+    <t>M999 208</t>
+  </si>
+  <si>
+    <t>M30</t>
+  </si>
+  <si>
+    <t>M50</t>
+  </si>
+  <si>
+    <t>M60</t>
+  </si>
+  <si>
+    <t>M65</t>
+  </si>
+  <si>
+    <t>M70</t>
+  </si>
+  <si>
+    <t>M75</t>
+  </si>
+  <si>
+    <t>M80</t>
+  </si>
+  <si>
+    <t>M85</t>
+  </si>
+  <si>
+    <t>M55 182</t>
+  </si>
+  <si>
+    <t>M61 198</t>
+  </si>
+  <si>
+    <t>M67 210</t>
+  </si>
+  <si>
+    <t>M73 223</t>
+  </si>
+  <si>
+    <t>M81 237</t>
+  </si>
+  <si>
+    <t>M89 249</t>
+  </si>
+  <si>
+    <t>M96 257</t>
+  </si>
+  <si>
+    <t>M102 265</t>
+  </si>
+  <si>
+    <t>M109 271</t>
+  </si>
+  <si>
+    <t>M999 284</t>
+  </si>
+  <si>
+    <t>agegroupscoring</t>
+  </si>
+  <si>
+    <t>agegroupbestathlete</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-  </numFmts>
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
@@ -627,7 +630,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="Calibri"/>
@@ -635,7 +638,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
@@ -658,7 +661,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -666,81 +669,28 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -799,62 +749,78 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285f4"/>
+        <a:srgbClr val="4285F4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ea4335"/>
+        <a:srgbClr val="EA4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="fbbc04"/>
+        <a:srgbClr val="FBBC04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34a853"/>
+        <a:srgbClr val="34A853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="ff6d01"/>
+        <a:srgbClr val="FF6D01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46bdc6"/>
+        <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155cc"/>
+        <a:srgbClr val="1155CC"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155cc"/>
+        <a:srgbClr val="1155CC"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -884,7 +850,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -908,7 +874,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -968,23 +934,22 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H27"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1005,14 +970,14 @@
       </c>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="4">
         <v>35</v>
       </c>
       <c r="D2" s="1"/>
@@ -1022,14 +987,14 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="4">
         <v>40</v>
       </c>
       <c r="D3" s="1"/>
@@ -1039,14 +1004,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="4">
         <v>45</v>
       </c>
       <c r="D4" s="1"/>
@@ -1054,446 +1019,446 @@
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="4">
         <v>49</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="4">
         <v>221</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="4">
         <v>55</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="4">
         <v>294</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="4">
         <v>264</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="4">
         <v>248</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="4">
         <v>61</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="4">
         <v>318</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="4">
         <v>293</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="4">
         <v>272</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="4">
         <v>67</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="4">
         <v>339</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="4">
         <v>328</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="4">
         <v>299</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="4">
         <v>73</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="4">
         <v>363</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="4">
         <v>347</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="4">
         <v>306</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="4">
         <v>81</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="4">
         <v>378</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="4">
         <v>372</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="4">
         <v>327</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="4">
         <v>89</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="4">
         <v>387</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="4">
         <v>371</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="4">
         <v>357</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="4">
         <v>96</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="4">
         <v>416</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="4">
         <v>397</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="4">
         <v>354</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="4">
         <v>102</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="4">
         <v>412</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="4">
         <v>392</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="4">
         <v>377</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="4">
         <v>109</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="4">
         <v>435</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="4">
         <v>417</v>
       </c>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="4">
         <v>999</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="4">
         <v>484</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="4">
         <v>432</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="4">
         <v>396</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="4">
         <v>35</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="4">
         <v>40</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="4">
         <v>135</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="4">
         <v>45</v>
       </c>
       <c r="D18" s="1"/>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="4">
         <v>179</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="4">
         <v>172</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="4">
         <v>49</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="4">
         <v>210</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="4">
         <v>206</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="4">
         <v>190</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="4">
         <v>55</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="4">
         <v>232</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="4">
         <v>211</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F20" s="4">
         <v>197</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="4">
         <v>59</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="4">
         <v>237</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="4">
         <v>228</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" s="4">
         <v>228</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="4">
         <v>64</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="4">
         <v>254</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="4">
         <v>240</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F22" s="4">
         <v>222</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="4">
         <v>71</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="4">
         <v>267</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="4">
         <v>252</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="4">
         <v>225</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="4">
         <v>76</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="4">
         <v>274</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="4">
         <v>259</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="4">
         <v>229</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="C25" s="4">
         <v>81</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="4">
         <v>283</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="4">
         <v>260</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F25" s="4">
         <v>231</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" s="4">
         <v>87</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="4">
         <v>294</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="4">
         <v>269</v>
       </c>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="4" t="n">
+      <c r="C27" s="4">
         <v>999</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="4">
         <v>330</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="4">
         <v>332</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F27" s="4">
         <v>255</v>
       </c>
       <c r="H27" s="1" t="s">
@@ -1502,31 +1467,25 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" location="Men" display="https://en.wikipedia.org/wiki/List_of_world_records_in_Olympic_weightlifting#Men"/>
-    <hyperlink ref="H3" r:id="rId2" location="Men" display="https://en.wikipedia.org/wiki/List_of_junior_world_records_in_Olympic_weightlifting#Men"/>
+    <hyperlink ref="H2" r:id="rId1" location="Men" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="H3" r:id="rId2" location="Men" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:U47"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:W47"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="23.29"/>
+    <col min="2" max="2" width="23.28515625" customWidth="1"/>
+    <col min="8" max="8" width="16.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1548,24 +1507,30 @@
       <c r="G1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-    </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+    </row>
+    <row r="2" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>44</v>
       </c>
@@ -1578,21 +1543,19 @@
       <c r="D2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4" t="n">
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
         <v>10</v>
       </c>
-      <c r="G2" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="G2" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -1604,8 +1567,10 @@
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+    </row>
+    <row r="3" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>47</v>
       </c>
@@ -1618,48 +1583,51 @@
       <c r="D3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="4">
         <v>10</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="4">
         <v>12</v>
       </c>
-      <c r="G3" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1" t="s">
+      <c r="G3" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+    </row>
+    <row r="4" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>56</v>
       </c>
@@ -1672,48 +1640,51 @@
       <c r="D4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="4">
         <v>11</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="4">
         <v>13</v>
       </c>
-      <c r="G4" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1" t="s">
+      <c r="G4" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
+        <v>188</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+    </row>
+    <row r="5" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>65</v>
       </c>
@@ -1726,48 +1697,51 @@
       <c r="D5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="4">
         <v>13</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="4">
         <v>15</v>
       </c>
-      <c r="G5" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1" t="s">
+      <c r="G5" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>188</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="P5" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="Q5" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="R5" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="S5" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+    </row>
+    <row r="6" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>75</v>
       </c>
@@ -1780,50 +1754,53 @@
       <c r="D6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="4">
         <v>12</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="4">
         <v>17</v>
       </c>
-      <c r="G6" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1" t="s">
+      <c r="G6" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>188</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="M6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="N6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="O6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="P6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="Q6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="R6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q6" s="1" t="s">
+      <c r="S6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R6" s="1" t="s">
+      <c r="T6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
       <c r="U6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+    </row>
+    <row r="7" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>76</v>
       </c>
@@ -1836,48 +1813,51 @@
       <c r="D7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="4">
         <v>12</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="4">
         <v>18</v>
       </c>
-      <c r="G7" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1" t="s">
+      <c r="G7" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>188</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="M7" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="N7" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="O7" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="P7" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="Q7" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="R7" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="S7" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+    </row>
+    <row r="8" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>86</v>
       </c>
@@ -1890,52 +1870,55 @@
       <c r="D8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="4">
         <v>17</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="4">
         <v>30</v>
       </c>
-      <c r="G8" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1" t="s">
+      <c r="G8" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>188</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="M8" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="N8" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="O8" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="P8" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="O8" s="1" t="s">
+      <c r="Q8" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="R8" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="Q8" s="1" t="s">
+      <c r="S8" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="R8" s="1" t="s">
+      <c r="T8" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="S8" s="1" t="s">
+      <c r="U8" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+    </row>
+    <row r="9" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>98</v>
       </c>
@@ -1948,52 +1931,55 @@
       <c r="D9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="4">
         <v>30</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="4">
         <v>34</v>
       </c>
-      <c r="G9" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1" t="s">
+      <c r="G9" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>188</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="M9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="N9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="O9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="P9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O9" s="1" t="s">
+      <c r="Q9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P9" s="1" t="s">
+      <c r="R9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q9" s="1" t="s">
+      <c r="S9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R9" s="1" t="s">
+      <c r="T9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S9" s="1" t="s">
+      <c r="U9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+    </row>
+    <row r="10" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
@@ -2006,52 +1992,52 @@
       <c r="D10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="4">
         <v>35</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="4">
         <v>39</v>
       </c>
-      <c r="G10" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1" t="s">
+      <c r="G10" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="N10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="O10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="P10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O10" s="1" t="s">
+      <c r="Q10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P10" s="1" t="s">
+      <c r="R10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q10" s="1" t="s">
+      <c r="S10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R10" s="1" t="s">
+      <c r="T10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S10" s="1" t="s">
+      <c r="U10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+    </row>
+    <row r="11" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
@@ -2064,52 +2050,52 @@
       <c r="D11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="4">
         <v>40</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="4">
         <v>44</v>
       </c>
-      <c r="G11" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1" t="s">
+      <c r="G11" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="M11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="N11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="O11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="P11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O11" s="1" t="s">
+      <c r="Q11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P11" s="1" t="s">
+      <c r="R11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q11" s="1" t="s">
+      <c r="S11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R11" s="1" t="s">
+      <c r="T11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S11" s="1" t="s">
+      <c r="U11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+    </row>
+    <row r="12" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>27</v>
       </c>
@@ -2122,52 +2108,55 @@
       <c r="D12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="4">
         <v>45</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="4">
         <v>49</v>
       </c>
-      <c r="G12" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1" t="s">
+      <c r="G12" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>188</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="M12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="N12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="O12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N12" s="1" t="s">
+      <c r="P12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O12" s="1" t="s">
+      <c r="Q12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P12" s="1" t="s">
+      <c r="R12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q12" s="1" t="s">
+      <c r="S12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R12" s="1" t="s">
+      <c r="T12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S12" s="1" t="s">
+      <c r="U12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+    </row>
+    <row r="13" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>101</v>
       </c>
@@ -2180,52 +2169,55 @@
       <c r="D13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="4">
         <v>50</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="4">
         <v>54</v>
       </c>
-      <c r="G13" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1" t="s">
+      <c r="G13" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
+        <v>188</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="N13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="O13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N13" s="1" t="s">
+      <c r="P13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O13" s="1" t="s">
+      <c r="Q13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P13" s="1" t="s">
+      <c r="R13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q13" s="1" t="s">
+      <c r="S13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R13" s="1" t="s">
+      <c r="T13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S13" s="1" t="s">
+      <c r="U13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+    </row>
+    <row r="14" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>29</v>
       </c>
@@ -2238,52 +2230,55 @@
       <c r="D14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="4">
         <v>55</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="4">
         <v>59</v>
       </c>
-      <c r="G14" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1" t="s">
+      <c r="G14" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
+        <v>188</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="M14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="N14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="O14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N14" s="1" t="s">
+      <c r="P14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O14" s="1" t="s">
+      <c r="Q14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P14" s="1" t="s">
+      <c r="R14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q14" s="1" t="s">
+      <c r="S14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R14" s="1" t="s">
+      <c r="T14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S14" s="1" t="s">
+      <c r="U14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+    </row>
+    <row r="15" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>102</v>
       </c>
@@ -2296,52 +2291,55 @@
       <c r="D15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="4">
         <v>60</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="4">
         <v>64</v>
       </c>
-      <c r="G15" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
+      <c r="G15" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
+        <v>188</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="M15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="N15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="O15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N15" s="1" t="s">
+      <c r="P15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O15" s="1" t="s">
+      <c r="Q15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P15" s="1" t="s">
+      <c r="R15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q15" s="1" t="s">
+      <c r="S15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R15" s="1" t="s">
+      <c r="T15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S15" s="1" t="s">
+      <c r="U15" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+    </row>
+    <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>103</v>
       </c>
@@ -2354,52 +2352,55 @@
       <c r="D16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="4">
         <v>65</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="4">
         <v>69</v>
       </c>
-      <c r="G16" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1" t="s">
+      <c r="G16" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H16" t="s">
+        <v>188</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="M16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="N16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="O16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N16" s="1" t="s">
+      <c r="P16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O16" s="1" t="s">
+      <c r="Q16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P16" s="1" t="s">
+      <c r="R16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q16" s="1" t="s">
+      <c r="S16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R16" s="1" t="s">
+      <c r="T16" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S16" s="1" t="s">
+      <c r="U16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V16" s="1"/>
+      <c r="W16" s="1"/>
+    </row>
+    <row r="17" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>104</v>
       </c>
@@ -2412,52 +2413,55 @@
       <c r="D17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="4">
         <v>70</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="4">
         <v>74</v>
       </c>
-      <c r="G17" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1" t="s">
+      <c r="G17" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H17" t="s">
+        <v>188</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="M17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L17" s="1" t="s">
+      <c r="N17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="O17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N17" s="1" t="s">
+      <c r="P17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O17" s="1" t="s">
+      <c r="Q17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P17" s="1" t="s">
+      <c r="R17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q17" s="1" t="s">
+      <c r="S17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R17" s="1" t="s">
+      <c r="T17" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S17" s="1" t="s">
+      <c r="U17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
+    </row>
+    <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>105</v>
       </c>
@@ -2470,52 +2474,55 @@
       <c r="D18" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="4">
         <v>75</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="4">
         <v>79</v>
       </c>
-      <c r="G18" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1" t="s">
+      <c r="G18" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H18" t="s">
+        <v>188</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="M18" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L18" s="1" t="s">
+      <c r="N18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M18" s="1" t="s">
+      <c r="O18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N18" s="1" t="s">
+      <c r="P18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O18" s="1" t="s">
+      <c r="Q18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P18" s="1" t="s">
+      <c r="R18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q18" s="1" t="s">
+      <c r="S18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R18" s="1" t="s">
+      <c r="T18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S18" s="1" t="s">
+      <c r="U18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
+    </row>
+    <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>106</v>
       </c>
@@ -2528,52 +2535,55 @@
       <c r="D19" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="4">
         <v>80</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="4">
         <v>84</v>
       </c>
-      <c r="G19" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1" t="s">
+      <c r="G19" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H19" t="s">
+        <v>188</v>
+      </c>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="M19" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L19" s="1" t="s">
+      <c r="N19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M19" s="1" t="s">
+      <c r="O19" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N19" s="1" t="s">
+      <c r="P19" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O19" s="1" t="s">
+      <c r="Q19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P19" s="1" t="s">
+      <c r="R19" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q19" s="1" t="s">
+      <c r="S19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R19" s="1" t="s">
+      <c r="T19" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S19" s="1" t="s">
+      <c r="U19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+    </row>
+    <row r="20" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>107</v>
       </c>
@@ -2586,52 +2596,55 @@
       <c r="D20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="4">
         <v>85</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F20" s="4">
         <v>999</v>
       </c>
-      <c r="G20" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1" t="s">
+      <c r="G20" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H20" t="s">
+        <v>188</v>
+      </c>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="M20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L20" s="1" t="s">
+      <c r="N20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M20" s="1" t="s">
+      <c r="O20" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N20" s="1" t="s">
+      <c r="P20" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O20" s="1" t="s">
+      <c r="Q20" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P20" s="1" t="s">
+      <c r="R20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q20" s="1" t="s">
+      <c r="S20" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R20" s="1" t="s">
+      <c r="T20" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S20" s="1" t="s">
+      <c r="U20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V20" s="1"/>
+      <c r="W20" s="1"/>
+    </row>
+    <row r="21" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>108</v>
       </c>
@@ -2644,52 +2657,55 @@
       <c r="D21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="4">
         <v>13</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" s="4">
         <v>17</v>
       </c>
-      <c r="G21" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1" t="s">
+      <c r="G21" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
+        <v>188</v>
+      </c>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="M21" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="N21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="O21" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N21" s="1" t="s">
+      <c r="P21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O21" s="1" t="s">
+      <c r="Q21" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P21" s="1" t="s">
+      <c r="R21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q21" s="1" t="s">
+      <c r="S21" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R21" s="1" t="s">
+      <c r="T21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
       <c r="U21" s="1"/>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V21" s="1"/>
+      <c r="W21" s="1"/>
+    </row>
+    <row r="22" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>111</v>
       </c>
@@ -2702,52 +2718,55 @@
       <c r="D22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="4">
         <v>15</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F22" s="4">
         <v>20</v>
       </c>
-      <c r="G22" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1" t="s">
+      <c r="G22" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H22" t="s">
+        <v>188</v>
+      </c>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="M22" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="N22" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="M22" s="1" t="s">
+      <c r="O22" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="N22" s="1" t="s">
+      <c r="P22" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="O22" s="1" t="s">
+      <c r="Q22" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="P22" s="1" t="s">
+      <c r="R22" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="Q22" s="1" t="s">
+      <c r="S22" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="R22" s="1" t="s">
+      <c r="T22" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="S22" s="1" t="s">
+      <c r="U22" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V22" s="1"/>
+      <c r="W22" s="1"/>
+    </row>
+    <row r="23" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>113</v>
       </c>
@@ -2760,52 +2779,55 @@
       <c r="D23" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="4">
         <v>15</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="4">
         <v>999</v>
       </c>
-      <c r="G23" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1" t="s">
+      <c r="G23" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H23" t="s">
+        <v>188</v>
+      </c>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="M23" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="N23" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="M23" s="1" t="s">
+      <c r="O23" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="N23" s="1" t="s">
+      <c r="P23" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="O23" s="1" t="s">
+      <c r="Q23" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="P23" s="1" t="s">
+      <c r="R23" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="Q23" s="1" t="s">
+      <c r="S23" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="R23" s="1" t="s">
+      <c r="T23" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="S23" s="1" t="s">
+      <c r="U23" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="V23" s="1"/>
+      <c r="W23" s="1"/>
+    </row>
+    <row r="24" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>125</v>
       </c>
@@ -2818,56 +2840,59 @@
       <c r="D24" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="4" t="n">
+      <c r="E24" s="4">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4">
         <v>999</v>
       </c>
-      <c r="G24" s="9" t="b">
-        <f aca="false">TRUE()</f>
+      <c r="G24" s="7" t="b">
+        <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" t="s">
+        <v>188</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="K24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="M24" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="N24" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="O24" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N24" s="1" t="s">
+      <c r="P24" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O24" s="1" t="s">
+      <c r="Q24" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P24" s="1" t="s">
+      <c r="R24" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q24" s="1" t="s">
+      <c r="S24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R24" s="1" t="s">
+      <c r="T24" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S24" s="1" t="s">
+      <c r="U24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-    </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
+    </row>
+    <row r="25" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>44</v>
       </c>
@@ -2880,21 +2905,19 @@
       <c r="D25" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="4" t="n">
+      <c r="E25" s="4">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4">
         <v>10</v>
       </c>
-      <c r="G25" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="1" t="s">
+      <c r="G25" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -2906,8 +2929,10 @@
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
-    </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+    </row>
+    <row r="26" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>47</v>
       </c>
@@ -2920,48 +2945,51 @@
       <c r="D26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="4">
         <v>10</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="F26" s="4">
         <v>12</v>
       </c>
-      <c r="G26" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1" t="s">
+      <c r="G26" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H26" t="s">
+        <v>188</v>
+      </c>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="L26" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="M26" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="N26" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="M26" s="1" t="s">
+      <c r="O26" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="N26" s="1" t="s">
+      <c r="P26" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="O26" s="1" t="s">
+      <c r="Q26" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="P26" s="1" t="s">
+      <c r="R26" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
       <c r="U26" s="1"/>
-    </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+    </row>
+    <row r="27" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>56</v>
       </c>
@@ -2974,48 +3002,51 @@
       <c r="D27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="4">
         <v>11</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F27" s="4">
         <v>13</v>
       </c>
-      <c r="G27" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1" t="s">
+      <c r="G27" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H27" t="s">
+        <v>188</v>
+      </c>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="L27" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="M27" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L27" s="1" t="s">
+      <c r="N27" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="M27" s="1" t="s">
+      <c r="O27" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="N27" s="1" t="s">
+      <c r="P27" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="O27" s="1" t="s">
+      <c r="Q27" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="P27" s="1" t="s">
+      <c r="R27" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
       <c r="U27" s="1"/>
-    </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
+    </row>
+    <row r="28" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>65</v>
       </c>
@@ -3028,46 +3059,49 @@
       <c r="D28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="4">
         <v>13</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="4">
         <v>15</v>
       </c>
-      <c r="G28" s="9" t="b">
-        <f aca="false">TRUE()</f>
+      <c r="G28" s="7" t="b">
+        <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1" t="s">
+      <c r="H28" t="s">
+        <v>188</v>
+      </c>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="M28" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="L28" s="1" t="s">
+      <c r="N28" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="M28" s="1" t="s">
+      <c r="O28" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="N28" s="1" t="s">
+      <c r="P28" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="O28" s="1" t="s">
+      <c r="Q28" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="P28" s="1" t="s">
+      <c r="R28" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="Q28" s="1" t="s">
+      <c r="S28" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-    </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+    </row>
+    <row r="29" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>75</v>
       </c>
@@ -3080,51 +3114,54 @@
       <c r="D29" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="4">
         <v>12</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" s="4">
         <v>17</v>
       </c>
-      <c r="G29" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1" t="s">
+      <c r="G29" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H29" t="s">
+        <v>188</v>
+      </c>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="M29" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L29" s="1" t="s">
+      <c r="N29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M29" s="1" t="s">
+      <c r="O29" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N29" s="1" t="s">
+      <c r="P29" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O29" s="1" t="s">
+      <c r="Q29" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P29" s="1" t="s">
+      <c r="R29" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q29" s="1" t="s">
+      <c r="S29" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R29" s="1" t="s">
+      <c r="T29" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S29" s="1" t="s">
+      <c r="U29" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="U29" s="1"/>
-    </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="W29" s="1"/>
+    </row>
+    <row r="30" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>76</v>
       </c>
@@ -3137,47 +3174,50 @@
       <c r="D30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="4">
         <v>12</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="4">
         <v>18</v>
       </c>
-      <c r="G30" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
+      <c r="G30" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H30" t="s">
+        <v>188</v>
+      </c>
       <c r="J30" s="1"/>
-      <c r="K30" s="1" t="s">
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="N30" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="M30" s="1" t="s">
+      <c r="O30" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="P30" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="O30" s="1" t="s">
+      <c r="Q30" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="P30" s="1" t="s">
+      <c r="R30" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="Q30" s="1" t="s">
+      <c r="S30" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="R30" s="1" t="s">
+      <c r="T30" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-    </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="V30" s="1"/>
+      <c r="W30" s="1"/>
+    </row>
+    <row r="31" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>86</v>
       </c>
@@ -3190,52 +3230,55 @@
       <c r="D31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="4">
         <v>17</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F31" s="4">
         <v>30</v>
       </c>
-      <c r="G31" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
+      <c r="G31" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H31" t="s">
+        <v>188</v>
+      </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
-      <c r="L31" s="1" t="s">
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="M31" s="1" t="s">
+      <c r="O31" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="N31" s="1" t="s">
+      <c r="P31" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="O31" s="1" t="s">
+      <c r="Q31" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="P31" s="1" t="s">
+      <c r="R31" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="Q31" s="1" t="s">
+      <c r="S31" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="R31" s="1" t="s">
+      <c r="T31" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="S31" s="1" t="s">
+      <c r="U31" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T31" s="1" t="s">
+      <c r="V31" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="U31" s="1" t="s">
+      <c r="W31" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>168</v>
       </c>
@@ -3248,52 +3291,55 @@
       <c r="D32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="4">
         <v>30</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" s="4">
         <v>34</v>
       </c>
-      <c r="G32" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
+      <c r="G32" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H32" t="s">
+        <v>188</v>
+      </c>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
-      <c r="L32" s="1" t="s">
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M32" s="1" t="s">
+      <c r="O32" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N32" s="1" t="s">
+      <c r="P32" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O32" s="1" t="s">
+      <c r="Q32" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P32" s="1" t="s">
+      <c r="R32" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q32" s="1" t="s">
+      <c r="S32" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R32" s="1" t="s">
+      <c r="T32" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S32" s="1" t="s">
+      <c r="U32" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T32" s="1" t="s">
+      <c r="V32" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="U32" s="1" t="s">
+      <c r="W32" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>6</v>
       </c>
@@ -3306,52 +3352,55 @@
       <c r="D33" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="4">
         <v>35</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" s="4">
         <v>39</v>
       </c>
-      <c r="G33" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
+      <c r="G33" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H33" t="s">
+        <v>188</v>
+      </c>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
-      <c r="L33" s="1" t="s">
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M33" s="1" t="s">
+      <c r="O33" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N33" s="1" t="s">
+      <c r="P33" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O33" s="1" t="s">
+      <c r="Q33" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P33" s="1" t="s">
+      <c r="R33" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q33" s="1" t="s">
+      <c r="S33" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R33" s="1" t="s">
+      <c r="T33" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S33" s="1" t="s">
+      <c r="U33" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T33" s="1" t="s">
+      <c r="V33" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="U33" s="1" t="s">
+      <c r="W33" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>9</v>
       </c>
@@ -3364,52 +3413,55 @@
       <c r="D34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="4">
         <v>40</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="F34" s="4">
         <v>44</v>
       </c>
-      <c r="G34" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
+      <c r="G34" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H34" t="s">
+        <v>188</v>
+      </c>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
-      <c r="L34" s="1" t="s">
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M34" s="1" t="s">
+      <c r="O34" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N34" s="1" t="s">
+      <c r="P34" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O34" s="1" t="s">
+      <c r="Q34" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P34" s="1" t="s">
+      <c r="R34" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q34" s="1" t="s">
+      <c r="S34" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R34" s="1" t="s">
+      <c r="T34" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S34" s="1" t="s">
+      <c r="U34" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T34" s="1" t="s">
+      <c r="V34" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="U34" s="1" t="s">
+      <c r="W34" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>11</v>
       </c>
@@ -3422,52 +3474,55 @@
       <c r="D35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="4">
         <v>45</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F35" s="4">
         <v>49</v>
       </c>
-      <c r="G35" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
+      <c r="G35" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H35" t="s">
+        <v>188</v>
+      </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
-      <c r="L35" s="1" t="s">
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M35" s="1" t="s">
+      <c r="O35" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N35" s="1" t="s">
+      <c r="P35" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O35" s="1" t="s">
+      <c r="Q35" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P35" s="1" t="s">
+      <c r="R35" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q35" s="1" t="s">
+      <c r="S35" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R35" s="1" t="s">
+      <c r="T35" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S35" s="1" t="s">
+      <c r="U35" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T35" s="1" t="s">
+      <c r="V35" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="U35" s="1" t="s">
+      <c r="W35" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>169</v>
       </c>
@@ -3480,52 +3535,55 @@
       <c r="D36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="4">
         <v>50</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="4">
         <v>54</v>
       </c>
-      <c r="G36" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
+      <c r="G36" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H36" t="s">
+        <v>188</v>
+      </c>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
-      <c r="L36" s="1" t="s">
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M36" s="1" t="s">
+      <c r="O36" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N36" s="1" t="s">
+      <c r="P36" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O36" s="1" t="s">
+      <c r="Q36" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P36" s="1" t="s">
+      <c r="R36" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q36" s="1" t="s">
+      <c r="S36" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R36" s="1" t="s">
+      <c r="T36" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S36" s="1" t="s">
+      <c r="U36" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T36" s="1" t="s">
+      <c r="V36" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="U36" s="1" t="s">
+      <c r="W36" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>13</v>
       </c>
@@ -3538,52 +3596,55 @@
       <c r="D37" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E37" s="4">
         <v>55</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="F37" s="4">
         <v>59</v>
       </c>
-      <c r="G37" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
+      <c r="G37" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H37" t="s">
+        <v>188</v>
+      </c>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-      <c r="L37" s="1" t="s">
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M37" s="1" t="s">
+      <c r="O37" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N37" s="1" t="s">
+      <c r="P37" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O37" s="1" t="s">
+      <c r="Q37" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P37" s="1" t="s">
+      <c r="R37" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q37" s="1" t="s">
+      <c r="S37" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R37" s="1" t="s">
+      <c r="T37" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S37" s="1" t="s">
+      <c r="U37" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T37" s="1" t="s">
+      <c r="V37" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="U37" s="1" t="s">
+      <c r="W37" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>170</v>
       </c>
@@ -3596,52 +3657,55 @@
       <c r="D38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="4" t="n">
+      <c r="E38" s="4">
         <v>60</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="F38" s="4">
         <v>64</v>
       </c>
-      <c r="G38" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
+      <c r="G38" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H38" t="s">
+        <v>188</v>
+      </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="L38" s="1" t="s">
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M38" s="1" t="s">
+      <c r="O38" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N38" s="1" t="s">
+      <c r="P38" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O38" s="1" t="s">
+      <c r="Q38" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P38" s="1" t="s">
+      <c r="R38" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q38" s="1" t="s">
+      <c r="S38" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R38" s="1" t="s">
+      <c r="T38" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S38" s="1" t="s">
+      <c r="U38" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T38" s="1" t="s">
+      <c r="V38" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="U38" s="1" t="s">
+      <c r="W38" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>171</v>
       </c>
@@ -3654,52 +3718,55 @@
       <c r="D39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="4">
         <v>65</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="F39" s="4">
         <v>69</v>
       </c>
-      <c r="G39" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
+      <c r="G39" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H39" t="s">
+        <v>188</v>
+      </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
-      <c r="L39" s="1" t="s">
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M39" s="1" t="s">
+      <c r="O39" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N39" s="1" t="s">
+      <c r="P39" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O39" s="1" t="s">
+      <c r="Q39" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P39" s="1" t="s">
+      <c r="R39" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q39" s="1" t="s">
+      <c r="S39" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R39" s="1" t="s">
+      <c r="T39" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S39" s="1" t="s">
+      <c r="U39" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T39" s="1" t="s">
+      <c r="V39" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="U39" s="1" t="s">
+      <c r="W39" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>172</v>
       </c>
@@ -3712,52 +3779,55 @@
       <c r="D40" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="E40" s="4">
         <v>70</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="F40" s="4">
         <v>74</v>
       </c>
-      <c r="G40" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
+      <c r="G40" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H40" t="s">
+        <v>188</v>
+      </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
-      <c r="L40" s="1" t="s">
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M40" s="1" t="s">
+      <c r="O40" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N40" s="1" t="s">
+      <c r="P40" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O40" s="1" t="s">
+      <c r="Q40" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P40" s="1" t="s">
+      <c r="R40" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q40" s="1" t="s">
+      <c r="S40" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R40" s="1" t="s">
+      <c r="T40" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S40" s="1" t="s">
+      <c r="U40" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T40" s="1" t="s">
+      <c r="V40" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="U40" s="1" t="s">
+      <c r="W40" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>173</v>
       </c>
@@ -3770,52 +3840,55 @@
       <c r="D41" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="4">
         <v>75</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="F41" s="4">
         <v>79</v>
       </c>
-      <c r="G41" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
+      <c r="G41" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H41" t="s">
+        <v>188</v>
+      </c>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
-      <c r="L41" s="1" t="s">
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M41" s="1" t="s">
+      <c r="O41" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N41" s="1" t="s">
+      <c r="P41" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O41" s="1" t="s">
+      <c r="Q41" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P41" s="1" t="s">
+      <c r="R41" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q41" s="1" t="s">
+      <c r="S41" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R41" s="1" t="s">
+      <c r="T41" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S41" s="1" t="s">
+      <c r="U41" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T41" s="1" t="s">
+      <c r="V41" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="U41" s="1" t="s">
+      <c r="W41" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>174</v>
       </c>
@@ -3828,52 +3901,55 @@
       <c r="D42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="4">
         <v>80</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="F42" s="4">
         <v>84</v>
       </c>
-      <c r="G42" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
+      <c r="G42" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H42" t="s">
+        <v>188</v>
+      </c>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
-      <c r="L42" s="1" t="s">
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M42" s="1" t="s">
+      <c r="O42" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N42" s="1" t="s">
+      <c r="P42" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O42" s="1" t="s">
+      <c r="Q42" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P42" s="1" t="s">
+      <c r="R42" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q42" s="1" t="s">
+      <c r="S42" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R42" s="1" t="s">
+      <c r="T42" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S42" s="1" t="s">
+      <c r="U42" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T42" s="1" t="s">
+      <c r="V42" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="U42" s="1" t="s">
+      <c r="W42" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>175</v>
       </c>
@@ -3886,52 +3962,55 @@
       <c r="D43" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" s="4">
         <v>85</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="F43" s="4">
         <v>999</v>
       </c>
-      <c r="G43" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
+      <c r="G43" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H43" t="s">
+        <v>188</v>
+      </c>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
-      <c r="L43" s="1" t="s">
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M43" s="1" t="s">
+      <c r="O43" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N43" s="1" t="s">
+      <c r="P43" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O43" s="1" t="s">
+      <c r="Q43" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P43" s="1" t="s">
+      <c r="R43" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q43" s="1" t="s">
+      <c r="S43" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R43" s="1" t="s">
+      <c r="T43" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S43" s="1" t="s">
+      <c r="U43" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T43" s="1" t="s">
+      <c r="V43" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="U43" s="1" t="s">
+      <c r="W43" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>108</v>
       </c>
@@ -3944,52 +4023,55 @@
       <c r="D44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E44" s="4" t="n">
+      <c r="E44" s="4">
         <v>13</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="F44" s="4">
         <v>17</v>
       </c>
-      <c r="G44" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
+      <c r="G44" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H44" t="s">
+        <v>188</v>
+      </c>
       <c r="J44" s="1"/>
-      <c r="K44" s="1" t="s">
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L44" s="1" t="s">
+      <c r="N44" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M44" s="1" t="s">
+      <c r="O44" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N44" s="1" t="s">
+      <c r="P44" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O44" s="1" t="s">
+      <c r="Q44" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P44" s="1" t="s">
+      <c r="R44" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q44" s="1" t="s">
+      <c r="S44" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R44" s="1" t="s">
+      <c r="T44" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S44" s="1" t="s">
+      <c r="U44" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T44" s="1" t="s">
+      <c r="V44" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="U44" s="1"/>
-    </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="W44" s="1"/>
+    </row>
+    <row r="45" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>111</v>
       </c>
@@ -4002,52 +4084,55 @@
       <c r="D45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="4">
         <v>15</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="F45" s="4">
         <v>20</v>
       </c>
-      <c r="G45" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
+      <c r="G45" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H45" t="s">
+        <v>188</v>
+      </c>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
-      <c r="L45" s="1" t="s">
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="M45" s="1" t="s">
+      <c r="O45" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="N45" s="1" t="s">
+      <c r="P45" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="O45" s="1" t="s">
+      <c r="Q45" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="P45" s="1" t="s">
+      <c r="R45" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="Q45" s="1" t="s">
+      <c r="S45" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="R45" s="1" t="s">
+      <c r="T45" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="S45" s="1" t="s">
+      <c r="U45" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T45" s="1" t="s">
+      <c r="V45" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="U45" s="1" t="s">
+      <c r="W45" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>113</v>
       </c>
@@ -4060,52 +4145,55 @@
       <c r="D46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E46" s="4">
         <v>15</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="F46" s="4">
         <v>999</v>
       </c>
-      <c r="G46" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
+      <c r="G46" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H46" t="s">
+        <v>188</v>
+      </c>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
-      <c r="L46" s="1" t="s">
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="M46" s="1" t="s">
+      <c r="O46" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="N46" s="1" t="s">
+      <c r="P46" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="O46" s="1" t="s">
+      <c r="Q46" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="P46" s="1" t="s">
+      <c r="R46" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="Q46" s="1" t="s">
+      <c r="S46" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="R46" s="1" t="s">
+      <c r="T46" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="S46" s="1" t="s">
+      <c r="U46" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="T46" s="1" t="s">
+      <c r="V46" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="U46" s="1" t="s">
+      <c r="W46" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>125</v>
       </c>
@@ -4118,66 +4206,64 @@
       <c r="D47" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="4" t="n">
+      <c r="E47" s="4">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4">
         <v>999</v>
       </c>
-      <c r="G47" s="9" t="b">
-        <f aca="false">TRUE()</f>
+      <c r="G47" s="7" t="b">
+        <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H47" t="s">
+        <v>188</v>
+      </c>
+      <c r="J47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I47" s="1" t="s">
+      <c r="K47" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J47" s="1" t="s">
+      <c r="L47" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K47" s="1" t="s">
+      <c r="M47" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L47" s="1" t="s">
+      <c r="N47" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M47" s="1" t="s">
+      <c r="O47" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N47" s="1" t="s">
+      <c r="P47" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O47" s="1" t="s">
+      <c r="Q47" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P47" s="1" t="s">
+      <c r="R47" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q47" s="1" t="s">
+      <c r="S47" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R47" s="1" t="s">
+      <c r="T47" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S47" s="1" t="s">
+      <c r="U47" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T47" s="1" t="s">
+      <c r="V47" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="U47" s="1" t="s">
+      <c r="W47" s="1" t="s">
         <v>22</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>